--- a/cell_sim/data/Mycoplasma_pneumoniae/input_data/complex_formation.xlsx
+++ b/cell_sim/data/Mycoplasma_pneumoniae/input_data/complex_formation.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,31 +460,3045 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Ribosome</t>
+          <t>DNA Gyrase complex</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MPN164,MPN190,MPN225,MPN189,MPN178,MPN622,MPN660,MPN174,MPN230,MPN169,MPN208,MPN541,MPN171,MPN446,MPN182,MPN228,MPN226,MPN179,MPN616,MPN220,MPN538,MPN219,MPN617,MPN175,MPN183,MPN172,MPN181,MPN658,MPN168,MPN117,MPN325,MPN170,MPN167,MPN327,MPN624,MPN173,MPN165,MPN360,MPN540,MPN471,MPN682,MPN166,MPN177,MPN180,MPN539,MPN231</t>
+          <t>MPN003,MPN004</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>46</v>
-      </c>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maier 2011 Table S7</t>
+          <t>Expasy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>median of direct-quantified copies/cell across r-proteins (Maier 2011 'n/d' rows excluded)</t>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Phenylalanine-tRNA synthetase complex</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MPN105,MPN106</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RNA polymerase complex</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MPN024,MPN191,MPN352,MPN516,MPN515</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1,1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Transcription antitermination factor complex</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MPN067,MPN024,MPN191,MPN352,MPN516,MPN515</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1,1,1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Bacillus subtilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Pyruvate dehydrogenase complex</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MPN390,MPN391,MPN392,MPN393</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Ribonucleoside-diphosphate reductase complex</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MPN322,MPN324</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>DNA Topoisomerase IV complex</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MPN122,MPN123</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DNA polymerase III complex</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MPN001,MPN007,MPN034,MPN378</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Translation elongation factor complex</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MPN450,MPN618,MPN631,MPN665,MPN573</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1,1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ribosome complex</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MPN069,MPN116,MPN117,MPN164,MPN165,MPN166,MPN167,MPN168,MPN169,MPN170,MPN171,MPN172,MPN173,MPN174,MPN175,MPN176,MPN177,MPN178,MPN179,MPN180,MPN181,MPN182,MPN183,MPN188,MPN189,MPN190,MPN192,MPN208,MPN219,MPN220,MPN225,MPN226,MPN228,MPN230,MPN231,MPN296,MPN325,MPN327,MPN360,MPN446,MPN471,MPN538,MPN539,MPN540,MPN541,MPN616,MPN617,MPN622,MPN624,MPN658,MPN660,MPN682</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cohesin-like complex</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MPN300,MPN301,MPN426</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RbfA-30S-ribosomal subunit complex</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MPN156</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PMID 15866174</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Thermus thermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Glycolytic enzyme complex 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MPN430,MPN674,MPN303,MPN302</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PMID 15701694</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Mus musculus</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DnaK-GrpE-DnaJ complex</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MPN434,MPN021,MPN120</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PMID 15632130</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Glycolytic enzyme complex 2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MPN025,MPN429,MPN606,MPN303</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PMID 8613464</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to MCF-7 cells (eukaryotes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Era-30S-ribosomal subunit complex</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MPN568</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PMID 15866174</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Thermus thermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>GreA-RNA polymerase complex</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>MPN401,MPN024,MPN191,MPN352,MPN516,MPN515</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1,1,1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PMID 17207814</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Dihydrofolate reductase-thymidylate synthase complex</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MPN321,MPN320</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Holliday junction ATP-dependent helicase complex</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MPN535,MPN536</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Aspartyl-glutamyl-tRNA(Asn/Gln) amidotransferase complex</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MPN236,MPN237,MPN238</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UvrABC complex</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MPN125,MPN619,MPN211</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Phosphotransfer system maltose complex</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MPN053,MPN651,MPN653</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1,1,1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PMID 17803963</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DnaB-DnaG complex</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MPN232,MPN353</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PMID 17947583</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Phosphotransfer system glucose complex</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MPN053,MPN207</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Phosphotransfer system fructose complex</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MPN053,MPN078</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Phosphotransfer system Ula (ascorbate) complex</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MPN053,MPN494,MPN495,MPN496</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1,1,1,1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>tRNA modification complex</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MPN557,MPN008</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PMID 17062623</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 i) heteromultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cell division MraZ</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MPN314</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Pyruvate kinase</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MPN303</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Thymidylate synthase</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MPN320</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>L-lactate dehydrogenase</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>MPN674</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fructose-biphosphate aldolase</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>MPN025</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cell division FtsZ; multiple, aggregates to form a ring-like structure</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>MPN317</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PMID 17977836</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HPr kinase/phosphorylase</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>MPN223</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>6-phosphofructokinase / Phosphohexokinase; multiple</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>MPN302</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PMID 16289704</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FMN-dependent NADH-azoreductase</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>MPN479</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PMID 16664776</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Glyceraldehyde-3-phosphate dehydrogenase</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MPN430</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Acetate kinase; 2 to 4 copies</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>MPN533</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PMID 21667429037</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Veillonella alcalescens</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Alanyl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MPN419</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Expasy / PMID 9207019</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermus thermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Probable inorganic polyphosphate/ATP-NAD kinase</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>MPN267</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PMID 11006082</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Mycobacterium flavus / tuberculosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Recombinase A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>MPN490</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PMID 17955055</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chaperone protein ClpB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>MPN531</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Replicative DNA helicase</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>MPN232</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PMID 17947583</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Glycerol kinase; 2 to 4 copies</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>MPN050</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PMID 9930671</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Putative proline iminopeptidase; multiple</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>MPN022</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>PMID 8885412</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Xanthomonas campestris pv. citri</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Methionyl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>MPN023</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>PMID 2126467</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Enolase</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>MPN606</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Putative Metallophosphoesterase</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>MPN126</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>PMID 17586769</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Single stranded DNA binding protein</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>MPN229</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>PMID 16041080</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Mycobacterium smegmatis</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Arginine deiminase-like protein; 2 to 3 copies</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>MPN560</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PMID 1722335911911465</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Lactococcus lactis</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DNA polymerase III subunit beta</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>MPN001</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Streptococcus pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DNA gyrase subunit B (homomultimer)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>MPN003</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>PMID 11850422</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermus thermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Thymidylate kinase</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>MPN006</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>PMID 11071809</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Homo sapiens</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Uncharacterized protein MG007 homolog</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>MPN007</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>PMID 11545747</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Pyrococcus furiosus</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DNA polymerase III polC-type</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>MPN034</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Deoxyribose-phosphate aldolase; 1 or 2 copies</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>MPN063</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>PMID 7675789</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Phosphomannomutase</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>MPN066</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>PMID 16540464</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Sulfolobus tokodaii</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Putative 1-phosphofructokinase</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>MPN079</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>PMID 2527305</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Homo sapiens</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Phenylalanyl-tRNA synthetase alpha chain</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>MPN105</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>PMID 7664121</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermus thermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Phenylalanyl-tRNA synthetase beta chain</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>MPN106</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>PMID 7664121</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermus thermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DNA-directed RNA polymerase subunit alpha</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>MPN191</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ribonucleoside-diphosphate reductase subunit beta</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>MPN322</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>PMID 16301799</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Salmonella typhimurium</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ribonucleoside-diphosphate reductase subunit alpha</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>MPN324</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>PMID 8052308</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Salmonella typhimurium</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Probable endonuclease 4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>MPN328</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>PMID 10458614</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Dihydrolipoyllysine-residue acetyltransferase</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>MPN391</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>PMID 9990008</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Pyruvate dehydrogenase E1 component beta</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>MPN392</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Pyruvate dehydrogenase E1 component alpha</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>MPN393</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Putative Xaa-Pro aminopeptidase</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>MPN470</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>PMID 12377124</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Pyrococcus horikoshii</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Probable L-ribulose-5-phosphate 3-epimerase UlaE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>MPN492</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>PMID 11732895</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Pseudomonas cichorii</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Probable thiamine biosynthesis protein</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>MPN550</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PMID 16343540</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Bacillus anthracis</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ribosomal RNA small subunit methyltransferase G</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>MPN558</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>PMID 18667428</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Geobacter sulfurreducens</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Probable NH3-dependent NAD+ synthetase</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>MPN562</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>PMID 15645437</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Bacillus subtilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>60 kDa chaperonin (GroEL); 2x7 = 14 copies</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>MPN573</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Putative type I restriction enzyme specificity protein</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>MPN638</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>PMID 16038930</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Methanocaldococcus jannaschii</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Elongation factor Tu</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>MPN665</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>PMID 16257965</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Dihydrolipoyl dehydrogenase</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MPN390</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>10 kDa chaperonin (GroES)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MPN574</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DNA topoisomerase 4 subunit B (homomultimer)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>MPN122</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>ATP-dependent protease Lon</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MPN332</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Probable tRNA modification GTPase (homomultimer)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MPN008</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermotoga maritima</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>UDP-galactopyranose mutase</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>MPN278</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>PMID 10089346</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Escherichia coli</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Uridylate kinase</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>MPN632</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>PMID 17297917</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Sulfolobus solfataricus</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Ribose-5-phosphate isomerase B</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>MPN595</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>PMID 15162497</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermotoga maritima</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Methionine aminopeptidase Peptidase M</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>MPN186</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>PMID 12297034</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Bacillus stearothermophilus</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>FAD synthetase</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MPN158</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>PMID 15468322</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Thermotoga maritima</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>GMP kinase</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MPN245</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>PMID 17012781</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Staphylococcus aureus</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Acyl carrier protein (ACP) synthetase</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>MPN298</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>PMID 16788183</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Adenine phosphoribosyltransferase</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MPN395</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>PMID 1039317011535055</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Leishmania donovani</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Threonyl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>MPN553</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Thymidine phosphorylase; multiple</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>MPN064</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Ribose-phosphate pyrophosphokinase; multiple</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>MPN073</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>PMID 2169413</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Bacillus subtilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Protein GrpE</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>MPN120</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>UDP-glucose 4-epimerase</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>MPN257</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tryptophanyl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>MPN265</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Replication initiator protein DnaA; multiple</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>MPN686</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>multiple</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>PMID 16829961</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; by homology to Aquifex aeolicus</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Triosephosphate isomerase</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>MPN629</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Serine hydroxymethyltransferase</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>MPN576</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Phosphoenolpyruvate-protein phosphotransferase</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>MPN627</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Glycyl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>MPN354</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Seryl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>MPN005</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Bifunctional protein FolD</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>MPN017</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Lysyl-tRNA synthetase</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>MPN277</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Histidyl-tRNA synthase</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>MPN045</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Thioredoxin reductase</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MPN240</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Chaperone protein DnaJ (homomultimer)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>MPN021</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Expasy</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Kuhner 2009 SOM Table S5 ii) homomultimers; M. pneumoniae by similarity</t>
         </is>
       </c>
     </row>

--- a/cell_sim/data/Mycoplasma_pneumoniae/input_data/complex_formation.xlsx
+++ b/cell_sim/data/Mycoplasma_pneumoniae/input_data/complex_formation.xlsx
@@ -473,7 +473,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="n">
+        <v>96</v>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -502,7 +504,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>23</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -531,7 +535,9 @@
           <t>1,1,1,1,1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>43</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -560,7 +566,9 @@
           <t>1,1,1,1,1,1</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="n">
+        <v>43</v>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -589,7 +597,9 @@
           <t>1,1,1,1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>249</v>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -618,7 +628,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>301</v>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -647,7 +659,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -676,7 +690,9 @@
           <t>1,1,1,1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -705,7 +721,9 @@
           <t>1,1,1,1,1</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>70</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -734,7 +752,9 @@
           <t>1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1,1</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="n">
+        <v>23</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -763,7 +783,9 @@
           <t>1,1,1</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>15</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -792,7 +814,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>PMID 15866174</t>
@@ -821,7 +845,9 @@
           <t>1,1,1,1</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="n">
+        <v>61</v>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>PMID 15701694</t>
@@ -850,7 +876,9 @@
           <t>1,1,1</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>73</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>PMID 15632130</t>
@@ -879,7 +907,9 @@
           <t>1,1,1,1</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>418</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>PMID 8613464</t>
@@ -908,7 +938,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="n">
+        <v>58</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>PMID 15866174</t>
@@ -937,7 +969,9 @@
           <t>1,1,1,1,1,1</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="n">
+        <v>43</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>PMID 17207814</t>
@@ -966,7 +1000,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="n">
+        <v>77</v>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1024,7 +1060,9 @@
           <t>1,1,1</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>9</v>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1053,7 +1091,9 @@
           <t>1,1,1</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="n">
+        <v>6</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1082,7 +1122,9 @@
           <t>1,1,1</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="n">
+        <v>11</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>PMID 17803963</t>
@@ -1111,7 +1153,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="n">
+        <v>14</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>PMID 17947583</t>
@@ -1140,7 +1184,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="n">
+        <v>474</v>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1169,7 +1215,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="n">
+        <v>2</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1198,7 +1246,9 @@
           <t>1,1,1,1</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="n">
+        <v>57</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1227,7 +1277,9 @@
           <t>1,1</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="n">
+        <v>22</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>PMID 17062623</t>
@@ -1256,7 +1308,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1285,7 +1339,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>104</v>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1314,7 +1370,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>108</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1343,7 +1401,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>259</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1372,7 +1432,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="n">
+        <v>599</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1401,7 +1463,9 @@
           <t>multiple</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>12</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>PMID 17977836</t>
@@ -1430,7 +1494,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1459,7 +1525,9 @@
           <t>multiple</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="n">
+        <v>61</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>PMID 16289704</t>
@@ -1488,7 +1556,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="n">
+        <v>297</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>PMID 16664776</t>
@@ -1517,7 +1587,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>557</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1546,7 +1618,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="n">
+        <v>178</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>PMID 21667429037</t>
@@ -1575,7 +1649,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="n">
+        <v>34</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>Expasy / PMID 9207019</t>
@@ -1604,7 +1680,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="n">
+        <v>165</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>PMID 11006082</t>
@@ -1662,7 +1740,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>15</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1691,7 +1771,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>PMID 17947583</t>
@@ -1720,7 +1802,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="n">
+        <v>55</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>PMID 9930671</t>
@@ -1749,7 +1833,9 @@
           <t>multiple</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="n">
+        <v>36</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>PMID 8885412</t>
@@ -1778,7 +1864,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>12</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>PMID 2126467</t>
@@ -1807,7 +1895,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>665</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1836,7 +1926,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>PMID 17586769</t>
@@ -1865,7 +1957,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>41</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>PMID 16041080</t>
@@ -1894,7 +1988,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>49</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>PMID 1722335911911465</t>
@@ -1923,7 +2019,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>132</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -1952,7 +2050,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="n">
+        <v>48</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>PMID 11850422</t>
@@ -1981,7 +2081,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>9</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>PMID 11071809</t>
@@ -2010,7 +2112,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>PMID 11545747</t>
@@ -2039,7 +2143,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>34</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2068,7 +2174,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>81</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>PMID 7675789</t>
@@ -2097,7 +2205,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>40</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>PMID 16540464</t>
@@ -2126,7 +2236,9 @@
           <t>8</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>PMID 2527305</t>
@@ -2155,7 +2267,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="n">
+        <v>32</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>PMID 7664121</t>
@@ -2184,7 +2298,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>11</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>PMID 7664121</t>
@@ -2213,7 +2329,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>236</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2242,7 +2360,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>228</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>PMID 16301799</t>
@@ -2271,7 +2391,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>150</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>PMID 8052308</t>
@@ -2300,7 +2422,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>132</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>PMID 10458614</t>
@@ -2329,7 +2453,9 @@
           <t>60</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>20</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>PMID 9990008</t>
@@ -2358,7 +2484,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>124</v>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2387,7 +2515,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>494</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2416,7 +2546,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>216</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>PMID 12377124</t>
@@ -2445,7 +2577,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>PMID 11732895</t>
@@ -2503,7 +2637,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>7</v>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>PMID 18667428</t>
@@ -2532,7 +2668,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>PMID 15645437</t>
@@ -2561,7 +2699,9 @@
           <t>14</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>155</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2590,7 +2730,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>192</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>PMID 16038930</t>
@@ -2619,7 +2761,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>1145</v>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>PMID 16257965</t>
@@ -2648,7 +2792,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>350</v>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2677,7 +2823,9 @@
           <t>7</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>183</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2706,7 +2854,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>4</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2735,7 +2885,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>30</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -2793,7 +2945,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>8</v>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>PMID 10089346</t>
@@ -2822,7 +2976,9 @@
           <t>6</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>PMID 17297917</t>
@@ -2851,7 +3007,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>6</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>PMID 15162497</t>
@@ -2880,7 +3038,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>PMID 12297034</t>
@@ -2909,7 +3069,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>5</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>PMID 15468322</t>
@@ -2938,7 +3100,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>84</v>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>PMID 17012781</t>
@@ -2996,7 +3160,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>12</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>PMID 1039317011535055</t>
@@ -3025,7 +3191,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>14</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3054,7 +3222,9 @@
           <t>multiple</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>149</v>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3083,7 +3253,9 @@
           <t>multiple</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>37</v>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>PMID 2169413</t>
@@ -3112,7 +3284,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>108</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3141,7 +3315,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>24</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3170,7 +3346,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>8</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3199,7 +3377,9 @@
           <t>multiple</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>55</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>PMID 16829961</t>
@@ -3228,7 +3408,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>31</v>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3257,7 +3439,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>102</v>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3286,7 +3470,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>42</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3315,7 +3501,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>66</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3344,7 +3532,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>40</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3373,7 +3563,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>6</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3402,7 +3594,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>86</v>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3431,7 +3625,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="n">
+        <v>5</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3460,7 +3656,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>58</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>Expasy</t>
@@ -3489,7 +3687,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="n">
+        <v>36</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>Expasy</t>
